--- a/excel outputs/דוח נכסים לתאריך:11-09-2026.xlsx
+++ b/excel outputs/דוח נכסים לתאריך:11-09-2026.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="ממצאים" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="נכסים" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -26,48 +26,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00666666"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <i val="1"/>
-      <color rgb="00444444"/>
-      <sz val="9"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001F4E79"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E8F4FD"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -75,81 +45,13 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="001F4E79"/>
-      </left>
-      <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001F4E79"/>
-      </bottom>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001F4E79"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="001F4E79"/>
-      </right>
-      <top style="thin">
-        <color rgb="001F4E79"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="001F4E79"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -515,20 +417,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="34" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="28" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="42" customWidth="1" min="8" max="8"/>
-  </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
           <t>שם העסק</t>
@@ -567,35 +459,10 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>קישור 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>לא נמצאו עסקים מאומתים בכתובות שנסרקו בהפעלה זו</t>
-        </is>
-      </c>
-      <c r="B2" s="3" t="n"/>
-      <c r="C2" s="3" t="n"/>
-      <c r="D2" s="3" t="n"/>
-      <c r="E2" s="3" t="n"/>
-      <c r="F2" s="3" t="n"/>
-      <c r="G2" s="3" t="n"/>
-      <c r="H2" s="4" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>סריקה: אינדקס 18254 (עבודת ישראל 17, ירושלים) | תקציב 30,000 טוקנים מוצה | 0 עסקים אומתו | בית מגורים — ייתכן עסקים שאינם ברשומות ציבוריות</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A2:H2"/>
-  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>